--- a/data/capstone-commute-mode-by-region.xlsx
+++ b/data/capstone-commute-mode-by-region.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sampling" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19210,4 +19211,70 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A teaching dataset written for the book. It holds a stratified survey of residents about how they get to work or study, and the residents and their answers are made up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Question: is commute mode related to the kind of area a resident lives in (Urban Core, Inner Suburb, Outer Suburb or Rural)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Design: 200 residents were drawn at random from each area type, so the area totals do not reflect population shares. The Sampling sheet has the details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>This export is deliberately raw. The area labels arrive in mixed case, two rows are duplicated, and five responses are missing the area or the commute mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cleaning guide: standardize the area label, drop duplicate rows, then drop responses missing either of the two variables under test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Age and the 1-to-7 commute satisfaction rating are carried for a check near the end of the notebook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>